--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f45324dec331549297ee971</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Jatafe club de gafe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>JAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Jatafe</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f45324dec331549297ee971</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jatafe club de gafe</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAT</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jatafe</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Mikelona 🐐</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47ab5b9e2edb0bb831c703</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bichos  team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bichos Team</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bichos FC</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f47ab5b9e2edb0bb831c703</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Mikelona 🐐</t>
+          <t>Bichos  team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>Bichos Team</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Bichos FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Mikelona 🐐</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unión Raulética de Santanguissa URSS</t>
+          <t>FC Mikelona 🐐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>URS</t>
+          <t>MIK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URSS</t>
+          <t>FC Mikelona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raulético de Madroto</t>
+          <t>Tactilona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC Mikelona 🐐</t>
+          <t>Unión Raulética de Santanguissa URSS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIK</t>
+          <t>URS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Mikelona</t>
+          <t>URSS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tactilona</t>
+          <t>Raulético de Madroto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/datos/maestros/md_propietarios.xlsx
+++ b/datos/maestros/md_propietarios.xlsx
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pallejandro S.A.D</t>
+          <t>🇧🇷Real Dendryd 🇧🇷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pallejandro</t>
+          <t>Real Dendryd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alejandro Lotina</t>
+          <t>Deninho</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🇧🇷Real Dendryd 🇧🇷</t>
+          <t>Pallejandro S.A.D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Real Dendryd</t>
+          <t>Pallejandro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deninho</t>
+          <t>Alejandro Lotina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f4531e9764e7d491e029746</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cracklos F.C</t>
+          <t>Cruyffisme FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Solrac24</t>
+          <t>Mister Seijames</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4531e9764e7d491e029746</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruyffisme FC</t>
+          <t>Cracklos F.C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mister Seijames</t>
+          <t>Solrac24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
